--- a/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_C.B. ZARAGOZA.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_C.B. ZARAGOZA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,31 +553,31 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>13.9197</v>
+        <v>14.8032</v>
       </c>
       <c r="E2" t="n">
-        <v>8.4581</v>
+        <v>9.341699999999999</v>
       </c>
       <c r="F2" t="n">
         <v>5.4615</v>
       </c>
       <c r="G2" t="n">
-        <v>6.0174</v>
+        <v>6.901</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6155</v>
+        <v>3.9073</v>
       </c>
       <c r="I2" t="n">
-        <v>2.402</v>
+        <v>2.9938</v>
       </c>
       <c r="J2" t="n">
-        <v>7.0863</v>
+        <v>7.9699</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7582</v>
+        <v>5.05</v>
       </c>
       <c r="L2" t="n">
-        <v>2.3283</v>
+        <v>2.920100000000001</v>
       </c>
       <c r="M2" t="n">
         <v>-1.0689</v>
@@ -1087,7 +1087,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. MUÑOZ SAMATAN</t>
+          <t>P. ASO JIMENEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1096,76 +1096,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8835999999999999</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8835999999999999</v>
+        <v>-3.4181</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3.5381</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8835999999999999</v>
+        <v>0.6985</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2918</v>
+        <v>-0.09269999999999978</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5918</v>
+        <v>0.7914000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8835999999999999</v>
+        <v>2.2513</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2918</v>
+        <v>1.8488</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5918</v>
+        <v>0.4025</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-1.5527</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-1.9415</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.3888</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.2054999999999998</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-5.3425</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>5.5481</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.1132</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.3269000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.4402</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.8973</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.8973</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. ASO JIMENEZ</t>
+          <t>A. ETXEGUREN GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1177,73 +1177,73 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1199999999999999</v>
+        <v>-1.6952</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4181</v>
+        <v>-4.3783</v>
       </c>
       <c r="F10" t="n">
-        <v>3.5381</v>
+        <v>2.6831</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6985</v>
+        <v>-1.0907</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.09269999999999978</v>
+        <v>-0.2330000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7914000000000001</v>
+        <v>-0.8577999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2513</v>
+        <v>2.0725</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8488</v>
+        <v>2.6236</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4025</v>
+        <v>-0.5511999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5527</v>
+        <v>-3.1632</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.9415</v>
+        <v>-2.8567</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3888</v>
+        <v>-0.3065999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2054999999999998</v>
+        <v>-1.849400000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.3425</v>
+        <v>-7.808299999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>5.5481</v>
+        <v>5.959</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1132</v>
+        <v>3.3613</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3269000000000001</v>
+        <v>1.6866</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4402</v>
+        <v>1.6749</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8973</v>
+        <v>-2.116400000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.3288000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8973</v>
+        <v>-1.7877</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ETXEGUREN GONZALEZ</t>
+          <t>D. ARJOL LOPEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,73 +1255,73 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6952</v>
+        <v>-1.732400000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3783</v>
+        <v>2.567099999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6831</v>
+        <v>-4.299499999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0907</v>
+        <v>5.262</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2330000000000001</v>
+        <v>4.7842</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8577999999999999</v>
+        <v>0.4776</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0725</v>
+        <v>8.819699999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6236</v>
+        <v>6.6475</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5511999999999999</v>
+        <v>2.1722</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.1632</v>
+        <v>-3.5577</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.8567</v>
+        <v>-1.8632</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3065999999999999</v>
+        <v>-1.6945</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.849400000000001</v>
+        <v>-1.2328</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.808299999999999</v>
+        <v>-8.6302</v>
       </c>
       <c r="R11" t="n">
-        <v>5.959</v>
+        <v>7.3973</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3613</v>
+        <v>-0.8300000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6866</v>
+        <v>0.1105</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6749</v>
+        <v>-0.9406</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.116400000000001</v>
+        <v>-4.9315</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3288000000000001</v>
+        <v>2.267</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7877</v>
+        <v>-7.1986</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. ARJOL LOPEZ</t>
+          <t>D. SANTOLARIA MORENO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1330,76 +1330,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.732400000000001</v>
+        <v>-2.0981</v>
       </c>
       <c r="E12" t="n">
-        <v>2.567099999999999</v>
+        <v>-1.1151</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.299499999999999</v>
+        <v>-0.983</v>
       </c>
       <c r="G12" t="n">
-        <v>5.262</v>
+        <v>-0.2603</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7842</v>
+        <v>-0.4416</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4776</v>
+        <v>0.1814</v>
       </c>
       <c r="J12" t="n">
-        <v>8.819699999999999</v>
+        <v>0.0395</v>
       </c>
       <c r="K12" t="n">
-        <v>6.6475</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2.1722</v>
+        <v>0.0395</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.5577</v>
+        <v>-0.2997</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.8632</v>
+        <v>-0.4416</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6945</v>
+        <v>0.1419</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.2328</v>
+        <v>-1.0274</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8.6302</v>
+        <v>-1.0274</v>
       </c>
       <c r="R12" t="n">
-        <v>7.3973</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8300000000000001</v>
+        <v>-0.2214</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1105</v>
+        <v>-0.1271</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9406</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.9315</v>
+        <v>-0.589</v>
       </c>
       <c r="W12" t="n">
-        <v>2.267</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.1986</v>
+        <v>-0.589</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. SANTOLARIA MORENO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1408,147 +1408,69 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.0981</v>
+        <v>50.25469999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.1151</v>
+        <v>25.8416</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.983</v>
+        <v>24.4129</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2603</v>
+        <v>41.843</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4416</v>
+        <v>24.9694</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1814</v>
+        <v>16.8735</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0395</v>
+        <v>61.07109999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>39.2587</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0395</v>
+        <v>21.8126</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2997</v>
+        <v>-19.2282</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4416</v>
+        <v>-14.2891</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1419</v>
+        <v>-4.938900000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.0274</v>
+        <v>-10.274</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0274</v>
+        <v>-64.7266</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>54.4526</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2214</v>
+        <v>8.0421</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1271</v>
+        <v>3.5458</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.09420000000000001</v>
+        <v>4.4968</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.589</v>
+        <v>10.6436</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>25.9516</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.589</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>C.B. ZARAGOZA</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>50.25479999999999</v>
-      </c>
-      <c r="E14" t="n">
-        <v>25.8416</v>
-      </c>
-      <c r="F14" t="n">
-        <v>24.4129</v>
-      </c>
-      <c r="G14" t="n">
-        <v>41.84300000000001</v>
-      </c>
-      <c r="H14" t="n">
-        <v>24.96939999999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>16.8735</v>
-      </c>
-      <c r="J14" t="n">
-        <v>61.07109999999999</v>
-      </c>
-      <c r="K14" t="n">
-        <v>39.2587</v>
-      </c>
-      <c r="L14" t="n">
-        <v>21.8126</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-19.2282</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-14.2891</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-4.938900000000001</v>
-      </c>
-      <c r="P14" t="n">
-        <v>-10.274</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-64.7266</v>
-      </c>
-      <c r="R14" t="n">
-        <v>54.4526</v>
-      </c>
-      <c r="S14" t="n">
-        <v>8.0421</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.5458</v>
-      </c>
-      <c r="U14" t="n">
-        <v>4.4968</v>
-      </c>
-      <c r="V14" t="n">
-        <v>10.6436</v>
-      </c>
-      <c r="W14" t="n">
-        <v>25.9516</v>
-      </c>
-      <c r="X14" t="n">
         <v>-15.308</v>
       </c>
     </row>
